--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBD09F99-91CA-40FF-A0FC-F275B97568B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{608CDC4D-BF46-4576-84BD-3AC955E9EA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{608CDC4D-BF46-4576-84BD-3AC955E9EA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2434E77F-241F-4CFA-96D1-6D4A4FE0E12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2434E77F-241F-4CFA-96D1-6D4A4FE0E12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8BCE6A9-A925-4E5D-9915-DB2DC03B29BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8BCE6A9-A925-4E5D-9915-DB2DC03B29BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A6CB737-D3B0-47C6-B38A-DDEA7B2CF6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A6CB737-D3B0-47C6-B38A-DDEA7B2CF6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45F321B0-09D9-4F52-9709-C9270F65F2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45F321B0-09D9-4F52-9709-C9270F65F2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFDAECFE-2100-49A5-8630-7C1120BCF969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFDAECFE-2100-49A5-8630-7C1120BCF969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{017843CE-4469-45C5-A7F9-33C9253B86BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{017843CE-4469-45C5-A7F9-33C9253B86BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18E93BDE-5BA3-4002-9BD1-346658A4A401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18E93BDE-5BA3-4002-9BD1-346658A4A401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22AFFC87-3530-405A-9557-F50571EB91C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
